--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -1,46 +1,155 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="comunas" sheetId="1" r:id="rId1"/>
+    <sheet name="Comunas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Metadata" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comunas'!$A$1:$I$11</definedName>
+  </definedNames>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t xml:space="preserve">Comuna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preescolar (tasa neta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Básica (tasa neta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media (tasa neta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superior (tasa neta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preescolar (tasa bruta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Básica (tasa bruta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Media (tasa bruta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Superior (tasa bruta, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coyhaique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lago Verde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aysén</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guaitecas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cochrane</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Higgins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tortel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chile Chico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Ibáñez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Campo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fecha de creación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27 20:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fuente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIT - MDSF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imagen asociada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comunal_e_matricula_a_2021_aysen.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indicador</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Unidad territorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Año</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00135A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,21 +157,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -112,10 +237,6 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -141,15 +262,12 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -175,6 +293,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -350,338 +469,394 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="13.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="27.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="23.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="22.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="25.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="28.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="24.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="23.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="26.71" hidden="0" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Comuna</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>E_PREBRUT_a</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASBRUT_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIABRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPBRUT_a</t>
-        </is>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Coyhaique</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>70.51782</v>
-      </c>
-      <c r="C2">
-        <v>96.15072000000001</v>
-      </c>
-      <c r="D2">
-        <v>84.23283000000001</v>
-      </c>
-      <c r="E2">
-        <v>43.9076</v>
-      </c>
-      <c r="F2">
-        <v>70.64793</v>
-      </c>
-      <c r="G2">
-        <v>100.6506</v>
-      </c>
-      <c r="H2">
-        <v>115.5976</v>
-      </c>
-      <c r="I2">
-        <v>70.34325</v>
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>70.52</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>96.15</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>84.23</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>43.91</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>70.65</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>100.65</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>70.34</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Lago Verde</t>
-        </is>
-      </c>
-      <c r="B3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="n">
         <v>68.75</v>
       </c>
-      <c r="D3">
-        <v>86.48649</v>
-      </c>
-      <c r="E3">
-        <v>46.37681</v>
-      </c>
-      <c r="F3">
-        <v>71.875</v>
-      </c>
-      <c r="H3">
-        <v>108.1081</v>
-      </c>
-      <c r="I3">
-        <v>71.0145</v>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2" t="n">
+        <v>86.49</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>71.88</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="n">
+        <v>108.11</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>71.01</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>70.7239</v>
-      </c>
-      <c r="C4">
-        <v>97.01956</v>
-      </c>
-      <c r="D4">
-        <v>81.44009</v>
-      </c>
-      <c r="E4">
-        <v>37.78838</v>
-      </c>
-      <c r="F4">
-        <v>70.98014000000001</v>
-      </c>
-      <c r="G4">
-        <v>102.049</v>
-      </c>
-      <c r="H4">
-        <v>112.9112</v>
-      </c>
-      <c r="I4">
-        <v>61.57518</v>
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>70.72</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>97.02</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>70.98</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>102.05</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>112.91</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>61.58</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cisnes</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>96.80231999999999</v>
-      </c>
-      <c r="D5">
-        <v>90.54877</v>
-      </c>
-      <c r="E5">
-        <v>45.93496</v>
-      </c>
-      <c r="G5">
-        <v>100.436</v>
-      </c>
-      <c r="H5">
-        <v>117.3781</v>
-      </c>
-      <c r="I5">
-        <v>64.02439</v>
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>45.93</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="n">
+        <v>100.44</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>117.38</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>64.02</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Guaitecas</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>72.16495</v>
-      </c>
-      <c r="C6">
-        <v>96.92308</v>
-      </c>
-      <c r="D6">
-        <v>90.52632</v>
-      </c>
-      <c r="E6">
-        <v>31.21387</v>
-      </c>
-      <c r="F6">
-        <v>72.16495</v>
-      </c>
-      <c r="G6">
-        <v>98.97436</v>
-      </c>
-      <c r="H6">
-        <v>106.3158</v>
-      </c>
-      <c r="I6">
-        <v>41.6185</v>
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>90.53</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>31.21</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>98.97</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>41.62</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Cochrane</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>73.41772</v>
-      </c>
-      <c r="C7">
-        <v>98.80669</v>
-      </c>
-      <c r="D7">
-        <v>81.86529</v>
-      </c>
-      <c r="E7">
-        <v>42.57143</v>
-      </c>
-      <c r="F7">
-        <v>73.41772</v>
-      </c>
-      <c r="G7">
-        <v>104.0573</v>
-      </c>
-      <c r="H7">
-        <v>108.2902</v>
-      </c>
-      <c r="I7">
-        <v>63.14286</v>
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>73.42</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>98.81</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>81.87</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>42.57</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>73.42</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>104.06</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>108.29</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>63.14</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>O Higgins</t>
-        </is>
-      </c>
-      <c r="D8">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="E8">
-        <v>33.96227</v>
-      </c>
-      <c r="H8">
-        <v>185.7143</v>
-      </c>
-      <c r="I8">
-        <v>52.83019</v>
+      <c r="E8" s="2" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2" t="n">
+        <v>185.71</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>52.83</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Tortel</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>95.38461</v>
-      </c>
-      <c r="D9">
-        <v>91.42856999999999</v>
-      </c>
-      <c r="E9">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>91.43</v>
+      </c>
+      <c r="E9" s="2" t="n">
         <v>47.5</v>
       </c>
-      <c r="G9">
-        <v>98.46154</v>
-      </c>
-      <c r="H9">
-        <v>97.14286</v>
-      </c>
-      <c r="I9">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="n">
+        <v>98.46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>97.14</v>
+      </c>
+      <c r="I9" s="2" t="n">
         <v>77.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Chile Chico</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>74.55197</v>
-      </c>
-      <c r="C10">
-        <v>94.90334</v>
-      </c>
-      <c r="D10">
-        <v>82.62411</v>
-      </c>
-      <c r="E10">
-        <v>37.96096</v>
-      </c>
-      <c r="F10">
-        <v>74.55197</v>
-      </c>
-      <c r="G10">
-        <v>100.1758</v>
-      </c>
-      <c r="H10">
-        <v>109.2199</v>
-      </c>
-      <c r="I10">
-        <v>62.90672</v>
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>94.9</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>82.62</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>37.96</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>74.55</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>100.18</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>62.91</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Río Ibáñez</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>74.35898</v>
-      </c>
-      <c r="C11">
-        <v>97.61904</v>
-      </c>
-      <c r="D11">
-        <v>91.22807</v>
-      </c>
-      <c r="E11">
-        <v>34.0249</v>
-      </c>
-      <c r="F11">
-        <v>74.35897</v>
-      </c>
-      <c r="G11">
-        <v>100.3968</v>
-      </c>
-      <c r="H11">
-        <v>118.4211</v>
-      </c>
-      <c r="I11">
-        <v>53.52697</v>
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>97.62</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>91.23</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34.02</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>100.4</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>118.42</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>53.53</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I11"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="24.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="60.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 20:09</t>
+    <t xml:space="preserve">2026-08-02 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:53</t>
+    <t xml:space="preserve">2026-08-05 10:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:48</t>
+    <t xml:space="preserve">2026-08-16 09:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:57</t>
+    <t xml:space="preserve">2026-08-19 12:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 12:52</t>
+    <t xml:space="preserve">2026-08-28 11:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2021_aysen.xlsx
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:48</t>
+    <t xml:space="preserve">2026-09-06 17:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
